--- a/Status.xlsx
+++ b/Status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\jaya sri\A_Project_related\Daily_Status_\Daily_Standup_Status2_\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{446FF3DF-E1E8-4985-8566-BC293A34A017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BFB798C-BB5D-487E-A689-A2784C366BEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="69">
   <si>
     <t>Date</t>
   </si>
@@ -223,6 +223,15 @@
   </si>
   <si>
     <t xml:space="preserve">powerbi architecture </t>
+  </si>
+  <si>
+    <t>power bi architecture and power bi admin  related videos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">project meeting </t>
+  </si>
+  <si>
+    <t>power bi (up stream , downstream, data flow, power bi admin,microsoft admin, reporting,power bi related microsoft tools )</t>
   </si>
 </sst>
 </file>
@@ -562,11 +571,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="103.109375" customWidth="1"/>
+    <col min="2" max="2" width="109.6640625" customWidth="1"/>
     <col min="3" max="3" width="15.6640625" customWidth="1"/>
     <col min="4" max="4" width="12.6640625" customWidth="1"/>
     <col min="5" max="5" width="12.5546875" customWidth="1"/>
@@ -1199,6 +1208,39 @@
         <v>65</v>
       </c>
       <c r="E62" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A63" s="3">
+        <v>45674</v>
+      </c>
+      <c r="B63" t="s">
+        <v>66</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A64" s="3">
+        <v>45677</v>
+      </c>
+      <c r="B64" t="s">
+        <v>67</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A65" s="3">
+        <v>45677</v>
+      </c>
+      <c r="B65" t="s">
+        <v>68</v>
+      </c>
+      <c r="E65" s="1" t="s">
         <v>33</v>
       </c>
     </row>

--- a/Status.xlsx
+++ b/Status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\jaya sri\A_Project_related\Daily_Status_\Daily_Standup_Status2_\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BFB798C-BB5D-487E-A689-A2784C366BEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59376309-A083-4C10-9957-17DAE884F3A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="74">
   <si>
     <t>Date</t>
   </si>
@@ -232,6 +232,21 @@
   </si>
   <si>
     <t>power bi (up stream , downstream, data flow, power bi admin,microsoft admin, reporting,power bi related microsoft tools )</t>
+  </si>
+  <si>
+    <t>1.installed tableau public in team pc.</t>
+  </si>
+  <si>
+    <t>2.supply chain management.</t>
+  </si>
+  <si>
+    <t>3.power bi administration explanation to team.</t>
+  </si>
+  <si>
+    <t>4.(a)Tableau metadata(difference between continuous vs discrete).</t>
+  </si>
+  <si>
+    <t>(b)Tableau (Naming conventions, rename).</t>
   </si>
 </sst>
 </file>
@@ -571,7 +586,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.6640625" style="1" customWidth="1"/>
@@ -1241,6 +1256,49 @@
         <v>68</v>
       </c>
       <c r="E65" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A66" s="3">
+        <v>45678</v>
+      </c>
+      <c r="B66" t="s">
+        <v>69</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B67" t="s">
+        <v>70</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B68" t="s">
+        <v>71</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B69" t="s">
+        <v>72</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B70" t="s">
+        <v>73</v>
+      </c>
+      <c r="E70" s="1" t="s">
         <v>33</v>
       </c>
     </row>

--- a/Status.xlsx
+++ b/Status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\jaya sri\A_Project_related\Daily_Status_\Daily_Standup_Status2_\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59376309-A083-4C10-9957-17DAE884F3A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{763FE1E5-D8EF-4AA5-BF60-0590F73446D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9732" yWindow="516" windowWidth="13308" windowHeight="8004" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Jayasri" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="76">
   <si>
     <t>Date</t>
   </si>
@@ -247,6 +247,12 @@
   </si>
   <si>
     <t>(b)Tableau (Naming conventions, rename).</t>
+  </si>
+  <si>
+    <t>Power bi task(generating login delay graph) -- completed</t>
+  </si>
+  <si>
+    <t>2.leave details graph -- in progress</t>
   </si>
 </sst>
 </file>
@@ -586,7 +592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.6640625" style="1" customWidth="1"/>
@@ -1271,6 +1277,9 @@
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A67" s="3">
+        <v>45678</v>
+      </c>
       <c r="B67" t="s">
         <v>70</v>
       </c>
@@ -1279,6 +1288,9 @@
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A68" s="3">
+        <v>45678</v>
+      </c>
       <c r="B68" t="s">
         <v>71</v>
       </c>
@@ -1287,6 +1299,9 @@
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A69" s="3">
+        <v>45678</v>
+      </c>
       <c r="B69" t="s">
         <v>72</v>
       </c>
@@ -1295,11 +1310,27 @@
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A70" s="3">
+        <v>45678</v>
+      </c>
       <c r="B70" t="s">
         <v>73</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>33</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A71" s="3">
+        <v>45679</v>
+      </c>
+      <c r="B71" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B72" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/Status.xlsx
+++ b/Status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\jaya sri\A_Project_related\Daily_Status_\Daily_Standup_Status2_\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{763FE1E5-D8EF-4AA5-BF60-0590F73446D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47A6BA20-A4AB-4AEA-ACE3-C81539755C9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9732" yWindow="516" windowWidth="13308" windowHeight="8004" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Jayasri" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="77">
   <si>
     <t>Date</t>
   </si>
@@ -253,6 +253,9 @@
   </si>
   <si>
     <t>2.leave details graph -- in progress</t>
+  </si>
+  <si>
+    <t>power bi graph and table creation</t>
   </si>
 </sst>
 </file>
@@ -592,7 +595,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.6640625" style="1" customWidth="1"/>
@@ -1327,10 +1330,27 @@
       <c r="B71" t="s">
         <v>74</v>
       </c>
+      <c r="E71" s="1" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B72" t="s">
         <v>75</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A73" s="3">
+        <v>45680</v>
+      </c>
+      <c r="B73" t="s">
+        <v>76</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/Status.xlsx
+++ b/Status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\jaya sri\A_Project_related\Daily_Status_\Daily_Standup_Status2_\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47A6BA20-A4AB-4AEA-ACE3-C81539755C9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C205A46-0F3E-4BDF-A715-4D3198F0923C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="78">
   <si>
     <t>Date</t>
   </si>
@@ -256,6 +256,9 @@
   </si>
   <si>
     <t>power bi graph and table creation</t>
+  </si>
+  <si>
+    <t>refresh error in power bi documentation prepare</t>
   </si>
 </sst>
 </file>
@@ -595,7 +598,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.6640625" style="1" customWidth="1"/>
@@ -1350,6 +1353,14 @@
         <v>76</v>
       </c>
       <c r="E73" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B74" t="s">
+        <v>77</v>
+      </c>
+      <c r="E74" s="1" t="s">
         <v>33</v>
       </c>
     </row>
